--- a/paper_tables/Table_5_Actual_vs_Predicted_formation_energy.xlsx
+++ b/paper_tables/Table_5_Actual_vs_Predicted_formation_energy.xlsx
@@ -89,16 +89,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,136 +465,2807 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Actual formation_energy</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Predicted formation_energy</t>
+          <t>Chemical Family</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Abs Error</t>
+          <t>DFT Actual [eV/atom]</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Rel Error (%)</t>
+          <t>CGCNN Predicted [eV/atom]</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Absolute Error |Δ|</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="D2" s="3" t="n">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Carbides</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.23802</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.268845390378307</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>NbC</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Carbides</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-0.52754</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>-0.585969330537371</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0.058</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>FeOF</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-1.72093</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>-1.510969024956381</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Rb2F</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-1.84711</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>-1.792209184770039</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>CuMoO4</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-1.6327</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>-1.671529083826328</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.039</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>NbF3</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-2.69514</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>-2.70096631301255</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>0.006</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>2.501</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>FeOF</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>-1.721</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>-1.745</v>
-      </c>
-      <c r="D3" s="5" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>HoBrO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-3.11975</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>-3.26913121540734</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.149</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Mn2F7</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>-2.05748</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>-1.749261480747622</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.308</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>MnF4</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>-2.27007</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>-2.254908134488431</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>YMg5</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Intermetallics/Alloys</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-0.02181</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0.05451014107945619</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.076</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Semimetals</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.16663</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.2532740994540222</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>TmBrO</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>-3.09072</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>-3.069967847148415</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.021</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>HgF2</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-1.39914</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>-1.314835835837208</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>As2Pt</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-0.48214</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>-0.6769318114553058</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.195</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Mg2SiO4</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-2.66738</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>-2.653525525931906</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>BaV4O8</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>-2.45408</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>-2.372435967153051</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.082</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>SmZnPO</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>-1.84605</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>-1.788929960472633</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0.057</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>UBrO2</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>-2.83573</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>-2.899131659074616</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>NiSb2</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>-0.1832</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>-0.2353280278084654</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Na2I</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>-0.53526</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-0.4903972378905412</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>GaTeCl</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>-0.31173</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>-0.2831070111721373</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.029</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>P2Pt</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>-0.68546</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>-0.7716795822343444</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>GaTe</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>-0.35031</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>-0.4121360171630057</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>NaMgSb</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>-0.5751500000000001</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>-0.5734090642016726</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>TiTl2F6</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>-2.89474</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>-3.015927777974869</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0.121</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>VOF</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>-2.57675</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>-2.508238096454122</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>YClO</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>-2.59859</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>-2.651532917181471</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>InTeI</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>-0.4031</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>-0.5321172696951721</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0.129</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>CaPbI4</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>-1.18747</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>-1.146266185095516</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0.041</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Sr2FeBrO3</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>-2.38774</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>-2.360447842014668</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0.027</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>TePb</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>-0.41685</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>-0.41219330252432</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>TlPd2Se3</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-0.38275</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>-0.3704519915243578</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>NbI2O</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>-1.33465</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>-1.277195727333109</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.057</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>PdCl2</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>-0.44889</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>-0.5061142967407974</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>0.057</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>SnO</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>-1.42902</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>-1.21140646667283</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0.218</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Se</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>0.13368</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0.06510739548669739</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>VSe3</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>-0.23539</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>-0.1973178852603396</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Bi2Pt</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0.04235</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0.1350376463205923</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0.093</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Intermetallics/Alloys</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.2387</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0.3079604155336097</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>TeO3</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Oxychalcogenides</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>-0.84544</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>-0.7997687591445466</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0.046</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>UBr4</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>-1.35092</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>-1.360098915317352</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>HfS2</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>-1.70531</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>-1.650942180085226</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0.054</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>P2Pt</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>-0.68546</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>-0.6450610176815634</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>AgSb2F12</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>-2.07728</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>-2.024462619830353</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>ZrSe3</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>-1.1037</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>-1.088783654818446</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Bi2Pt</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>0.04235</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>-0.01479811344210943</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0.057</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>SnSe2</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>-0.33426</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>-0.2930571786233072</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0.041</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>TiBr3</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>-1.23487</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>-1.233829848649767</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>ScAs2</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>-0.72684</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>-0.7980011543700419</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Ag2Se</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>-0.06499000000000001</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0.0007748127995591964</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0.066</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>NaMgSb</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>-0.5751500000000001</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>-0.5372909900341165</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Mg(ReO4)2</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>-1.91706</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>-1.923228136753128</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Nb(SCl)2</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>-1.08553</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>-0.9946847487855521</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>0.091</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>-0.63798</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>-0.6923819777262793</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>0.054</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>AlPd5I2</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>-0.3509</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>-0.4288745336181857</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0.078</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>ZrBr3</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>-1.24148</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>-1.334157114295991</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0.093</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>FeC2O6</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>-1.17809</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>-1.306688658764898</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>0.129</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>CrO3</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>-1.70516</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>-1.653048699895536</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Sb2TeSe2</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>-0.23647</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>-0.3279076238264499</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>0.091</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>B2S</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>0.45373</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>0.3280209602317127</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>SbCl5</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>-0.59178</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>-0.6668060031932098</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Ga</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Intermetallics/Alloys</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>0.04287</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>0.07589247415491987</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>0.033</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Li2CeAs2</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>-1.03869</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>-1.074411196165362</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Ca(HO)2</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>-1.99357</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>-1.976253312833442</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>0.017</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>NaSbO2</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>-1.51753</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>-1.478932206780545</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0.039</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>SnF4</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>-2.38709</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>-2.235346561387684</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Al2S3</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>-1.22286</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>-1.260614549263155</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>AuS2</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>0.02501</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>-0.06066139984488898</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Cu2Te</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0.12454</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>0.1027720092341588</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Te2W</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>-0.03597</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>-0.05491548853920071</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>0.019</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>AsC</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0.76617</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>0.771312401527637</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>TiGeO3</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>-2.20488</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>-2.127809909660455</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>0.077</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>CrSe</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>-0.30108</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>-0.1847972738274147</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>NbS2</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>-1.08445</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>-1.021483231700604</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>SiP2</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>-0.13219</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>-0.1574115395712277</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>VPbClO3</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>-2.01368</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>-2.161958941207487</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0.148</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>TaS2</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>-1.14598</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>-1.108073366327057</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Hg2ClO</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>-0.28077</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>-0.2206575140608832</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>KAuSe2</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>-0.62449</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>-0.6624856248928764</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>CoI2</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>0.01733</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>-0.04296889314859917</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>NiS2</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>0.00882</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>-0.01081104928022964</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>ClF</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>-0.37725</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>-0.4040100988672758</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>0.027</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Ag2SO4</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Oxychalcogenides</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>-0.91061</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>-0.9783534974454724</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0.068</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>ZrO2</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>-3.64248</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>-3.62428320523167</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>0.018</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>SbClO</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>-0.91639</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>-0.8638657113092937</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Au2S</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>-0.04796</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>-0.03083250046958369</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>0.017</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>TmAgP2Se6</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>-0.54342</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>-0.6141285948960906</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>PbIF</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>-1.59793</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>-1.570214143240242</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Nb3SBr7</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>-1.05071</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>-1.028574736053599</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>LiBi4F20</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>-1.80548</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>-1.879033938738704</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>0.074</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Mg2Al2Se5</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>-1.11609</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>-1.208285400428772</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0.092</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>AgBiO2</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>-0.91121</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>-0.845035340077118</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>0.066</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>As2O3</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>-1.26178</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>-1.090264472853974</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>PbSe</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>-0.59552</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>-0.4909485796574058</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Nb2O5</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>-2.39579</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>-2.354034674750648</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>VSe</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>-0.5150400000000001</v>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>-0.4499586226104265</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Te2SO7</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Oxychalcogenides</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>-1.21068</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>-1.263687033096769</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>SiS</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>-0.38924</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>-0.3391866121787995</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>GaSe</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>-0.5815900000000001</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>-0.4011007119096018</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>BiBr3</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>-0.74825</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>-0.5310790408040151</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>0.217</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>PF5</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>-2.57302</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>-2.598784921296454</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>0.026</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>CN2</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="n">
+        <v>0.82056</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>0.8405994280276701</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>HgPS3</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>-0.15992</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>-0.2559437125644621</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>0.096</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>VS2</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="n">
+        <v>-0.94178</v>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>-1.004440263386899</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>SbI3</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>-0.3086</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>-0.4075560568702465</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>0.099</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>ZrS2</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>-1.68597</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>-1.784439145314716</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>0.098</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>PI3</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>-0.03756</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>-0.1028248227972351</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>ErAgP2Se6</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>-0.54348</v>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>-0.5646525466590364</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>0.021</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>PI2</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>-0.05037</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>-0.1160245854681368</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>0.066</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>BCl3</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>-0.9517099999999999</v>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>-1.047014279776212</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>0.095</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>NaHO</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>-1.39886</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>-1.375101226141345</v>
+      </c>
+      <c r="F112" s="2" t="n">
         <v>0.024</v>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>1.371</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>NbC</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>-0.528</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>-0.569</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>7.861</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>NbF3</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>-2.695</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>-2.766</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>2.617</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Rb2F</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>-1.847</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>-1.829</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.978</v>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>AgClO2</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="n">
+        <v>0.24216</v>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>0.2569307086825843</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>K(SbSe2)2</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>-0.52624</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>-0.5054493764601261</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>0.021</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>HfCl4</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>-1.87674</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>-1.814194170257815</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>LiCr9O27</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>-1.70516</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>-1.667272605549186</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>0.038</v>
       </c>
     </row>
   </sheetData>
